--- a/Smoke-tests/Smoke1 - Регистрация.xlsx
+++ b/Smoke-tests/Smoke1 - Регистрация.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaros\Documents\.Olimp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaros\Documents\Smoke-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D442925-92A2-40FC-8297-AE85971CFCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23475B53-FB63-4113-8492-423EC4B956FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="4065" windowWidth="23160" windowHeight="11685" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -74,12 +74,6 @@
 Минимальное разрешение экрана: 1280х1024</t>
   </si>
   <si>
-    <t>Выбрать роль «Покупатель».</t>
-  </si>
-  <si>
-    <t>Подтвердить регистрацию (нажав «Зарегистрироваться»).</t>
-  </si>
-  <si>
     <t>Поля принимают значения</t>
   </si>
   <si>
@@ -89,13 +83,7 @@
     <t>4 мин</t>
   </si>
   <si>
-    <t>Нажать на кнопку «Войти» .</t>
-  </si>
-  <si>
     <t>Отображается окно "Вход"</t>
-  </si>
-  <si>
-    <t>Переключиться на окно "Регистрация"</t>
   </si>
   <si>
     <t xml:space="preserve">Отображается окно "Регистрация"
@@ -103,9 +91,6 @@
   </si>
   <si>
     <t>Тестовые данные</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заполнить поля (Эл. почта, имя, телефон и дать слгласие). </t>
   </si>
   <si>
     <t>Эл. Почта - Test1@mail.ru
@@ -118,6 +103,21 @@
   </si>
   <si>
     <t>Перейти на сайт Строймаркета  https://stroymarket1.su.</t>
+  </si>
+  <si>
+    <t>1) Нажать на кнопку «Войти» .</t>
+  </si>
+  <si>
+    <t>2) Переключиться на окно "Регистрация"</t>
+  </si>
+  <si>
+    <t>3) Выбрать роль «Покупатель».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4) Заполнить поля (Эл. почта, имя, телефон и дать слгласие). </t>
+  </si>
+  <si>
+    <t>5) Подтвердить регистрацию (нажав «Зарегистрироваться»).</t>
   </si>
 </sst>
 </file>
@@ -785,7 +785,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>5</v>
@@ -808,17 +808,17 @@
         <v>9</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="225" customHeight="1" x14ac:dyDescent="0.25">
@@ -828,11 +828,11 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I3" s="7"/>
     </row>
@@ -843,11 +843,11 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -858,13 +858,13 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -875,11 +875,11 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I6" s="7"/>
     </row>
